--- a/ui-test/tests/data_excel/data_environments.xlsx
+++ b/ui-test/tests/data_excel/data_environments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2022_AutoTest\source-code\cbs-neptune-autotest\ui-test\tests\data_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8BEDCF9-906B-44CF-A8FE-EF6E4AAB0D3C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B6CC3EF-397D-48D2-BBDB-89C561C207E1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="833" activeTab="1" xr2:uid="{5E6CAB1F-32B9-4BCB-BBA6-02F8AECCA153}"/>
+    <workbookView xWindow="28680" yWindow="4455" windowWidth="20730" windowHeight="11310" tabRatio="833" activeTab="1" xr2:uid="{5E6CAB1F-32B9-4BCB-BBA6-02F8AECCA153}"/>
   </bookViews>
   <sheets>
     <sheet name="LIST_URL" sheetId="6" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="55">
   <si>
     <t>No</t>
   </si>
@@ -179,6 +179,24 @@
   </si>
   <si>
     <t>Running</t>
+  </si>
+  <si>
+    <t>autoteller005</t>
+  </si>
+  <si>
+    <t>automanager005</t>
+  </si>
+  <si>
+    <t>autoteller006</t>
+  </si>
+  <si>
+    <t>automanager006</t>
+  </si>
+  <si>
+    <t>194</t>
+  </si>
+  <si>
+    <t>104, 194</t>
   </si>
 </sst>
 </file>
@@ -237,7 +255,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -264,17 +282,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top/>
       <bottom/>
@@ -285,7 +292,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -293,8 +300,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -629,7 +635,7 @@
       <c r="C1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>47</v>
       </c>
     </row>
@@ -652,7 +658,7 @@
       <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>48</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -684,7 +690,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -698,15 +704,15 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{8C40CC63-E5F8-4B4D-BD8C-5321506997A6}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{442777CB-DBD7-45A1-8451-08A2EF654271}"/>
-    <hyperlink ref="B4" r:id="rId3" xr:uid="{B3090E0A-8E06-41D4-B260-7FE390D1E564}"/>
-    <hyperlink ref="B5" r:id="rId4" xr:uid="{71989EF6-D9F2-4E1D-8BA2-EE43595FEB11}"/>
-    <hyperlink ref="B6" r:id="rId5" xr:uid="{61204248-B58A-4EFC-9B11-679B32EB26D3}"/>
-    <hyperlink ref="E2" r:id="rId6" xr:uid="{275FC6AC-EB42-4068-9190-091C476EC5CC}"/>
-    <hyperlink ref="E3" r:id="rId7" xr:uid="{81192206-BF44-47CB-884D-B084B51B76D1}"/>
-    <hyperlink ref="E4" r:id="rId8" xr:uid="{18369CF6-371E-4D87-96EB-5247D714448F}"/>
-    <hyperlink ref="E5" r:id="rId9" xr:uid="{58233C47-21FD-4F6F-B594-F4A5042E2838}"/>
-    <hyperlink ref="E6" r:id="rId10" xr:uid="{2DF631CD-D303-4E21-8B0D-5D727F96E14A}"/>
+    <hyperlink ref="B4" r:id="rId2" xr:uid="{B3090E0A-8E06-41D4-B260-7FE390D1E564}"/>
+    <hyperlink ref="B5" r:id="rId3" xr:uid="{71989EF6-D9F2-4E1D-8BA2-EE43595FEB11}"/>
+    <hyperlink ref="B6" r:id="rId4" xr:uid="{61204248-B58A-4EFC-9B11-679B32EB26D3}"/>
+    <hyperlink ref="E2" r:id="rId5" xr:uid="{275FC6AC-EB42-4068-9190-091C476EC5CC}"/>
+    <hyperlink ref="E3" r:id="rId6" xr:uid="{81192206-BF44-47CB-884D-B084B51B76D1}"/>
+    <hyperlink ref="E4" r:id="rId7" xr:uid="{18369CF6-371E-4D87-96EB-5247D714448F}"/>
+    <hyperlink ref="E5" r:id="rId8" xr:uid="{58233C47-21FD-4F6F-B594-F4A5042E2838}"/>
+    <hyperlink ref="E6" r:id="rId9" xr:uid="{2DF631CD-D303-4E21-8B0D-5D727F96E14A}"/>
+    <hyperlink ref="B3" r:id="rId10" xr:uid="{A0024682-4637-434C-AAD5-3ABAA0652C7B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId11"/>
@@ -715,11 +721,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFA57D17-4F41-4432-8A64-4A68876EE8A2}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
@@ -1011,6 +1017,74 @@
       </c>
       <c r="E18" s="4" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
